--- a/data/trans_orig/P43-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43-Clase-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2007 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123063</t>
+          <t>122946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158433</t>
+          <t>157999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>140288</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>123063</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>158433</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>52,02%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>158</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164293</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181635</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146148</t>
+          <t>146582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181518</t>
+          <t>181635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>164293</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>146148</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>181518</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>47,98%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304581</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>304581</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>304581</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>304581</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115302</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98881</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135015</t>
+          <t>132287</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>115302</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>98881</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>135015</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254585</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>234872</t>
+          <t>237600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>271006</t>
+          <t>273527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>254585</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>234872</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>271006</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>63,5%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>361</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369887</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369887</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369887</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>369887</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>369887</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>369887</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80912</t>
+          <t>80508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>68501</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>57103</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>80912</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>34,23%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98301</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85890</t>
+          <t>86294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109699</t>
+          <t>110280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>98301</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>85890</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>109699</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>58,93%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>51,49%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>65,77%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166802</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166802</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166802</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166802</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166802</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>237292</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213313</t>
+          <t>212625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262009</t>
+          <t>262353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>237292</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>213313</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>262009</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>33,35%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>474308</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>498975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449591</t>
+          <t>449247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498287</t>
+          <t>498975</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>474308</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>449591</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>498287</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>66,65%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>711600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>711600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>711600</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>711600</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>711600</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>711600</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204614</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184190</t>
+          <t>180153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>228093</t>
+          <t>227169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>204614</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>184190</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>228093</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>32,51%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>338</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>361958</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>386419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338479</t>
+          <t>339403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>382382</t>
+          <t>386419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>361958</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>338479</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>382382</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>63,89%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>537</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566572</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566572</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>566572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>566572</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>566572</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>566572</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2438,37 +1853,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507445</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>472880</t>
+          <t>473089</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>542512</t>
+          <t>540262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>507445</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>472880</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>542512</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>40,96%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>38,17%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1931,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>726</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>731534</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>698717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>765890</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>696467</t>
+          <t>698717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>766099</t>
+          <t>765890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>731534</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>696467</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>766099</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>61,83%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2009,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238979</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238979</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1238979</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2728,41 +2073,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1238979</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1238979</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1238979</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2781,37 +2091,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273442</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1218883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1330341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1215183</t>
+          <t>1218883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1329841</t>
+          <t>1330341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,47 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1273442</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1215183</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1329841</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2169,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2084979</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2028080</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2139538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2028580</t>
+          <t>2028080</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2143238</t>
+          <t>2139538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,47 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2084979</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2028580</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2143238</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -3007,37 +2247,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3358421</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3358421</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3358421</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3071,41 +2311,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3276</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3358421</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3358421</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3358421</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3119,7 +2324,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3127,7 +2332,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3142,7 +2346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3161,25 +2365,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2012 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +2387,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3199,17 +2396,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3280,41 +2466,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3337,13 +2488,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3358,37 +2502,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135471</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116235</t>
+          <t>116687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153299</t>
+          <t>154791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,47 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>135471</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>116235</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>153299</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -3471,37 +2580,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>178983</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161155</t>
+          <t>159663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198219</t>
+          <t>197767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,47 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>178983</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>161155</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>198219</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>51,25%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -3584,37 +2658,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3648,41 +2722,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>314454</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3701,37 +2740,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129727</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110357</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149272</t>
+          <t>148654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,47 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>129727</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>110357</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>149272</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>39,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -3814,37 +2818,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202928</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>183383</t>
+          <t>184001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222298</t>
+          <t>221176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,47 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>202928</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>183383</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>222298</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>61,0%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
+          <t>66,49%</t>
         </is>
       </c>
     </row>
@@ -3927,37 +2896,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332655</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3991,41 +2960,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>332655</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>332655</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>332655</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4044,37 +2978,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134417</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116429</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150763</t>
+          <t>150670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,47 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>134417</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>116429</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>150763</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>52,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>58,43%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -4157,37 +3056,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107279</t>
+          <t>107372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141613</t>
+          <t>138788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,47 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>123625</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>107279</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>141613</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>41,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -4270,37 +3134,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258042</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4334,41 +3198,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>258042</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>258042</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>258042</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4387,37 +3216,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302624</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>276953</t>
+          <t>275535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332246</t>
+          <t>330960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,47 +3276,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>302624</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>276953</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>332246</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -4500,37 +3294,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459932</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>431596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>430310</t>
+          <t>431596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>485603</t>
+          <t>487021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,47 +3354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>459932</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>430310</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>485603</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>60,31%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -4613,37 +3372,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>707</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>762556</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4677,41 +3436,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>762556</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>762556</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>762556</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4730,37 +3454,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>391154</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363004</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>363171</t>
+          <t>363004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>421621</t>
+          <t>417369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,47 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>391154</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>363171</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>421621</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>47,94%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>55,66%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3532,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366379</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>394529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>335912</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394362</t>
+          <t>394529</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,47 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>366379</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>335912</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>394362</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>44,34%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>52,06%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -4956,37 +3610,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5020,41 +3674,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>757533</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>757533</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>757533</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5073,37 +3692,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>531</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570784</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>536389</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>606905</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>538307</t>
+          <t>536389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>605260</t>
+          <t>606905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,47 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>570784</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>538307</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>605260</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>51,7%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>48,76%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3770,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>533321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>497200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567716</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>498845</t>
+          <t>497200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>565798</t>
+          <t>567716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,47 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>533321</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>498845</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>565798</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>48,3%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
+          <t>51,42%</t>
         </is>
       </c>
     </row>
@@ -5299,37 +3848,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104105</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1104105</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5363,41 +3912,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1104105</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1104105</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1104105</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5416,37 +3930,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1664177</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1602670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1728341</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1602990</t>
+          <t>1602670</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1721689</t>
+          <t>1728341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,47 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1664177</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1602990</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1721689</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>47,15%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4008,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1865167</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1801003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1926674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1807655</t>
+          <t>1801003</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1926354</t>
+          <t>1926674</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,47 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1865167</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1807655</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1926354</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>52,85%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -5642,37 +4086,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529344</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529344</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3529344</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5706,41 +4150,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3529344</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3529344</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3529344</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5754,7 +4163,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -5762,7 +4171,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -5777,7 +4185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5796,25 +4204,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +4226,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5834,17 +4235,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5915,41 +4305,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5972,13 +4327,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5993,37 +4341,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170061</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152363</t>
+          <t>153130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>190046</t>
+          <t>188996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,47 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>170061</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>152363</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>190046</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>49,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>44,23%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>55,17%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -6106,37 +4419,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174395</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>154410</t>
+          <t>155460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>192093</t>
+          <t>191326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,47 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>174395</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>154410</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>192093</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>50,63%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>44,83%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -6219,37 +4497,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344456</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344456</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6283,41 +4561,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>344456</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>344456</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>344456</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6336,37 +4579,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172622</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153603</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154598</t>
+          <t>153603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>192511</t>
+          <t>193279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>172622</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>154598</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>192511</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>41,75%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>51,99%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -6449,37 +4657,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197649</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177760</t>
+          <t>176992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215673</t>
+          <t>216668</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>197649</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>177760</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>215673</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>48,01%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>58,25%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -6562,37 +4735,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370271</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370271</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6626,41 +4799,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>370271</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>370271</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>370271</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6679,37 +4817,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92972</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105449</t>
+          <t>104914</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,47 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>92972</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>80379</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>105449</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>48,39%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -6792,37 +4895,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73151</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>61209</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>87476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,47 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>73151</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>60674</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>85744</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>51,61%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -6905,37 +4973,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6969,41 +5037,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7022,37 +5055,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310358</t>
+          <t>310899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>370256</t>
+          <t>368592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>338774</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>310358</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>370256</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>44,99%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -7135,37 +5133,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>481</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>484202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>512077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>452720</t>
+          <t>454384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512618</t>
+          <t>512077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>484202</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>452720</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>512618</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>55,01%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -7248,37 +5211,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822976</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822976</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>822976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7312,41 +5275,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>822976</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>822976</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>822976</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7365,37 +5293,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>380</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417208</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>390008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>387358</t>
+          <t>390008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>444845</t>
+          <t>445306</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>417208</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>387358</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>444845</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>56,84%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>52,78%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>60,61%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -7478,37 +5371,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>315</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316734</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289097</t>
+          <t>288636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>346584</t>
+          <t>343934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>316734</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>289097</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>346584</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>43,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -7591,37 +5449,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>733942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>733942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>733942</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7655,41 +5513,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>733942</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>733942</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>733942</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7708,37 +5531,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>497</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559959</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>526843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>592718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>524412</t>
+          <t>526843</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591514</t>
+          <t>592718</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,47 +5591,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>559959</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>524412</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>591514</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -7821,37 +5609,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>483</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>509018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>477463</t>
+          <t>476259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>544565</t>
+          <t>542134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,47 +5669,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>509018</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>477463</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>544565</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>47,62%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>44,67%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -7934,37 +5687,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>980</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1068977</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1068977</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1068977</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7998,41 +5751,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1068977</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>1068977</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1068977</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8051,37 +5769,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1751596</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1689706</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1809311</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1690061</t>
+          <t>1689706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1812290</t>
+          <t>1809311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,47 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1751596</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1690061</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1812290</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>49,95%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>48,19%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -8164,37 +5847,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1755148</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1697433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1817038</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1694454</t>
+          <t>1697433</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1816683</t>
+          <t>1817038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,47 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1755148</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1694454</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1816683</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>48,32%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>51,81%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -8277,37 +5925,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506744</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506744</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3506744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8341,41 +5989,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>3506744</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>3506744</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3506744</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8389,7 +6002,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -8397,7 +6010,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -8412,7 +6024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8431,25 +6043,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023</t>
+          <t>Población según si le han realizado alguna vez una mamografía por prescripción de algún especialista en 2023 (tasa de respuesta: 99,26%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +6065,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8469,17 +6074,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8550,41 +6144,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8607,13 +6166,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8628,37 +6180,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189108</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +6225,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174818</t>
+          <t>173007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204439</t>
+          <t>204545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,47 +6240,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>189108</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>174818</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>204439</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>66,23%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -8741,37 +6258,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119567</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +6303,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104236</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133857</t>
+          <t>135668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,47 +6318,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>119567</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>104236</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>133857</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>33,77%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>43,36%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -8854,37 +6336,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308675</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8918,41 +6400,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>308675</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>308675</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>308675</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8971,37 +6418,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165764</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>152192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150733</t>
+          <t>152192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178619</t>
+          <t>181730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,47 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>165764</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>150733</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>178619</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>64,68%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -9084,37 +6496,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110377</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +6541,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97522</t>
+          <t>94411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125408</t>
+          <t>123949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,47 +6556,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>110377</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>97522</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>125408</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -9197,37 +6574,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9261,41 +6638,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>276141</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9314,37 +6656,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +6701,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66827</t>
+          <t>67029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84211</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,47 +6716,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>76182</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>66827</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>84211</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>71,29%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -9427,37 +6734,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41950</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +6779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51305</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,47 +6794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>41950</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>33921</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>51305</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -9540,37 +6812,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118132</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9604,41 +6876,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>118132</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>118132</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>118132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9657,37 +6894,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>369513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>632643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +6939,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>371223</t>
+          <t>369513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>656753</t>
+          <t>632643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,47 +6954,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>480976</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>371223</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>656753</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -9770,37 +6972,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282708</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>394171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +7017,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106931</t>
+          <t>131041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>392461</t>
+          <t>394171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,47 +7032,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>282708</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>106931</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>392461</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -9883,37 +7050,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>763684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>763684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>763684</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9947,41 +7114,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>763684</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>763684</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>763684</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10000,37 +7132,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355917</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +7177,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>245944</t>
+          <t>251837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>410465</t>
+          <t>405959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,47 +7192,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>355917</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>245944</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>410465</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -10113,37 +7210,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325608</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +7255,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>271060</t>
+          <t>275566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435581</t>
+          <t>429688</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,47 +7270,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>325608</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>271060</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>435581</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>47,78%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>63,91%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -10226,37 +7288,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681525</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681525</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10290,41 +7352,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>681525</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>681525</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>681525</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10343,37 +7370,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>545</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286186</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>308796</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +7415,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>262819</t>
+          <t>263673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>309977</t>
+          <t>308796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,47 +7430,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>286186</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>262819</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>309977</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>46,22%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>50,06%</t>
+          <t>49,87%</t>
         </is>
       </c>
     </row>
@@ -10456,37 +7448,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>386</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333050</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355563</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +7493,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309259</t>
+          <t>310440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>356417</t>
+          <t>355563</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,47 +7508,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>333050</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>309259</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>356417</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>53,78%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>49,94%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>57,56%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -10569,37 +7526,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>619236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>619236</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>619236</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10633,41 +7590,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>619236</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>619236</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>619236</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10686,37 +7608,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1554134</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1421905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1842768</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +7653,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1415761</t>
+          <t>1421905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1800715</t>
+          <t>1842768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +7668,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2415</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1554134</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1415761</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1800715</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>51,16%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -10799,37 +7686,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1213260</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>924626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1345489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +7731,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>966679</t>
+          <t>924626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1351633</t>
+          <t>1345489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +7746,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1530</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1213260</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>966679</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1351633</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>48,84%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -10912,37 +7764,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2767394</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2767394</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2767394</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10976,41 +7828,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2767394</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>2767394</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2767394</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -11024,7 +7841,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -11032,7 +7849,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P43-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P43-Clase-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122946</t>
+          <t>124041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122946</t>
+          <t>124041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146582</t>
+          <t>147528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181635</t>
+          <t>180540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146582</t>
+          <t>147528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181635</t>
+          <t>180540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96360</t>
+          <t>98501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132287</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96360</t>
+          <t>98501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132287</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237600</t>
+          <t>235593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273527</t>
+          <t>271386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237600</t>
+          <t>235593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273527</t>
+          <t>271386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80508</t>
+          <t>79842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80508</t>
+          <t>79842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>86960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110280</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>86960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110280</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>212625</t>
+          <t>213784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262353</t>
+          <t>263692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212625</t>
+          <t>213784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262353</t>
+          <t>263692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449247</t>
+          <t>447908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498975</t>
+          <t>497816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449247</t>
+          <t>447908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498975</t>
+          <t>497816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180153</t>
+          <t>182255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227169</t>
+          <t>228880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>180153</t>
+          <t>182255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>227169</t>
+          <t>228880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339403</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386419</t>
+          <t>384317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339403</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>386419</t>
+          <t>384317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>473089</t>
+          <t>476402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>540262</t>
+          <t>542098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>473089</t>
+          <t>476402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>540262</t>
+          <t>542098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>698717</t>
+          <t>696881</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>765890</t>
+          <t>762577</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>698717</t>
+          <t>696881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>765890</t>
+          <t>762577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1218883</t>
+          <t>1218012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1330341</t>
+          <t>1330056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1218883</t>
+          <t>1218012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1330341</t>
+          <t>1330056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2028080</t>
+          <t>2028365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2139538</t>
+          <t>2140409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2028080</t>
+          <t>2028365</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2139538</t>
+          <t>2140409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116687</t>
+          <t>118092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154791</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116687</t>
+          <t>118092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154791</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159663</t>
+          <t>159246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197767</t>
+          <t>196362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159663</t>
+          <t>159246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197767</t>
+          <t>196362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>109945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148654</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>109945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148654</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184001</t>
+          <t>184889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>221176</t>
+          <t>222710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184001</t>
+          <t>184889</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221176</t>
+          <t>222710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119254</t>
+          <t>118579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150670</t>
+          <t>151502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119254</t>
+          <t>118579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150670</t>
+          <t>151502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107372</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107372</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275535</t>
+          <t>275050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330960</t>
+          <t>330937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>275535</t>
+          <t>275050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>330960</t>
+          <t>330937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>431596</t>
+          <t>431619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>487021</t>
+          <t>487506</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431596</t>
+          <t>431619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487021</t>
+          <t>487506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>363004</t>
+          <t>364882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417369</t>
+          <t>419991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>363004</t>
+          <t>364882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417369</t>
+          <t>419991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -3542,12 +3542,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340164</t>
+          <t>337542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394529</t>
+          <t>392651</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3557,12 +3557,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340164</t>
+          <t>337542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394529</t>
+          <t>392651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>536389</t>
+          <t>538209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>606905</t>
+          <t>604499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>536389</t>
+          <t>538209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>606905</t>
+          <t>604499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>497200</t>
+          <t>499606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>567716</t>
+          <t>565896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>497200</t>
+          <t>499606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>567716</t>
+          <t>565896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1602670</t>
+          <t>1598664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1728341</t>
+          <t>1720806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1602670</t>
+          <t>1598664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1728341</t>
+          <t>1720806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1801003</t>
+          <t>1808538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1926674</t>
+          <t>1930680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1801003</t>
+          <t>1808538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1926674</t>
+          <t>1930680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153130</t>
+          <t>151086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188996</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153130</t>
+          <t>151086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188996</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>156397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191326</t>
+          <t>193370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155460</t>
+          <t>156397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191326</t>
+          <t>193370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153603</t>
+          <t>152079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193279</t>
+          <t>190956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>153603</t>
+          <t>152079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>193279</t>
+          <t>190956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176992</t>
+          <t>179315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>218192</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176992</t>
+          <t>179315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216668</t>
+          <t>218192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,93%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>105229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104914</t>
+          <t>105229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61209</t>
+          <t>60894</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>87797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61209</t>
+          <t>60894</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>87797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>310899</t>
+          <t>311463</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>368592</t>
+          <t>368416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310899</t>
+          <t>311463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>368592</t>
+          <t>368416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>454384</t>
+          <t>454560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512077</t>
+          <t>511513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454384</t>
+          <t>454560</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>512077</t>
+          <t>511513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390008</t>
+          <t>392440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445306</t>
+          <t>445644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390008</t>
+          <t>392440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>445306</t>
+          <t>445644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288636</t>
+          <t>288298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343934</t>
+          <t>341502</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>288636</t>
+          <t>288298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>343934</t>
+          <t>341502</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>526843</t>
+          <t>524044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>592718</t>
+          <t>593026</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526843</t>
+          <t>524044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>592718</t>
+          <t>593026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>476259</t>
+          <t>475951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>542134</t>
+          <t>544933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>476259</t>
+          <t>475951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>542134</t>
+          <t>544933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1689706</t>
+          <t>1692839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1809311</t>
+          <t>1811021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1689706</t>
+          <t>1692839</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1809311</t>
+          <t>1811021</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,64%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1697433</t>
+          <t>1695723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1817038</t>
+          <t>1813905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1697433</t>
+          <t>1695723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1817038</t>
+          <t>1813905</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -6185,32 +6185,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173007</t>
+          <t>192660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>224752</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6220,32 +6220,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>189108</t>
+          <t>209228</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173007</t>
+          <t>192660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>224752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -6263,32 +6263,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119567</t>
+          <t>128904</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104130</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135668</t>
+          <t>145472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6298,32 +6298,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119567</t>
+          <t>128904</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104130</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135668</t>
+          <t>145472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6376,17 +6376,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>338132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6423,32 +6423,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>152192</t>
+          <t>168269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>181730</t>
+          <t>200255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6458,32 +6458,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165764</t>
+          <t>184166</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152192</t>
+          <t>168269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>181730</t>
+          <t>200255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -6501,32 +6501,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>124885</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94411</t>
+          <t>108796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123949</t>
+          <t>140782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6536,32 +6536,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>110377</t>
+          <t>124885</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94411</t>
+          <t>108796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123949</t>
+          <t>140782</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -6579,17 +6579,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>276141</t>
+          <t>309051</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6661,32 +6661,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67029</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84427</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76182</t>
+          <t>82020</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67029</t>
+          <t>72271</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84427</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -6739,32 +6739,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>59135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6774,32 +6774,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>59135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -6817,17 +6817,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6852,17 +6852,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118132</t>
+          <t>131406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6899,32 +6899,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>369513</t>
+          <t>279064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>632643</t>
+          <t>321391</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6934,32 +6934,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>300765</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>369513</t>
+          <t>279064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>632643</t>
+          <t>321391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -6977,32 +6977,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>282708</t>
+          <t>322535</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131041</t>
+          <t>301909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>394171</t>
+          <t>344236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7012,32 +7012,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>282708</t>
+          <t>322535</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131041</t>
+          <t>301909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394171</t>
+          <t>344236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -7055,17 +7055,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7090,17 +7090,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>763684</t>
+          <t>623300</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7137,32 +7137,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251837</t>
+          <t>326336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>405959</t>
+          <t>372537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7172,32 +7172,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>355917</t>
+          <t>349723</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251837</t>
+          <t>326336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>405959</t>
+          <t>372537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -7215,32 +7215,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>325608</t>
+          <t>298545</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>275566</t>
+          <t>275731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>429688</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7250,32 +7250,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>325608</t>
+          <t>298545</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>275566</t>
+          <t>275731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>429688</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -7293,17 +7293,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7328,17 +7328,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>681525</t>
+          <t>648268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7360,7 +7360,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7375,32 +7375,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>285224</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>308796</t>
+          <t>334059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7410,32 +7410,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>286186</t>
+          <t>308336</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>263673</t>
+          <t>285224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>308796</t>
+          <t>334059</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -7453,32 +7453,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>333050</t>
+          <t>372821</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>310440</t>
+          <t>347098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>355563</t>
+          <t>395933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>333050</t>
+          <t>372821</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310440</t>
+          <t>347098</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>355563</t>
+          <t>395933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>619236</t>
+          <t>681157</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7613,32 +7613,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1554134</t>
+          <t>1434237</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1421905</t>
+          <t>1389628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1842768</t>
+          <t>1484717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7648,32 +7648,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1554134</t>
+          <t>1434237</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1421905</t>
+          <t>1389628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1842768</t>
+          <t>1484717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -7691,32 +7691,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1213260</t>
+          <t>1297076</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>924626</t>
+          <t>1246596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1345489</t>
+          <t>1341685</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7726,32 +7726,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1213260</t>
+          <t>1297076</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>924626</t>
+          <t>1246596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1345489</t>
+          <t>1341685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -7769,17 +7769,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2767394</t>
+          <t>2731313</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
